--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260615.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.56%</t>
+          <t>10.31%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.06%</t>
+          <t>10.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>6.44%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>111,374,000</t>
+          <t>184,738,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>184,738,000</t>
+          <t>111,374,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
@@ -748,14 +748,14 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>202606TX</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -814,95 +814,95 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>28,485,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>28,485,000</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>226,605,516</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>226,605,516</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -1144,24 +1144,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>49,897,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,110 +1173,110 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>49,897,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>14,243,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>85,399,080</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>85,399,080</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,352,969,392</t>
+          <t>10,562,195,309</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,014,846,022</t>
+          <t>10,637,547,248</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-2,133,639,432</t>
+          <t>-1,734,350,255</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
